--- a/src/test/resources/testData/dataTransferFondos.xlsx
+++ b/src/test/resources/testData/dataTransferFondos.xlsx
@@ -5,15 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DUOC\2 año\4to Semestre\Automatizacion de Pruebas\Altoro Testing\src\test\resources\testData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\savki\IdeaProjects\TestAltoroMutual\src\test\resources\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AE0A514-2EE4-4B29-AABE-409804E8A12C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8975179F-EF75-403D-9F92-3341C7047EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2892" yWindow="2892" windowWidth="17280" windowHeight="8880" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
+    <sheet name="Hoja3" sheetId="3" r:id="rId3"/>
+    <sheet name="Hoja4" sheetId="4" r:id="rId4"/>
+    <sheet name="Hoja5" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="33">
   <si>
     <t>Col A (0)</t>
   </si>
@@ -61,13 +65,76 @@
   </si>
   <si>
     <t>2000.0 was successfully transferred from Account 800001 into Account 800000</t>
+  </si>
+  <si>
+    <t>Usuario</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>Mensaje</t>
+  </si>
+  <si>
+    <t>leafar</t>
+  </si>
+  <si>
+    <t>savkita</t>
+  </si>
+  <si>
+    <t>rodri</t>
+  </si>
+  <si>
+    <t>Login Failed</t>
+  </si>
+  <si>
+    <t>Hello Admin User</t>
+  </si>
+  <si>
+    <t>12345</t>
+  </si>
+  <si>
+    <t>54321</t>
+  </si>
+  <si>
+    <t>1837</t>
+  </si>
+  <si>
+    <t>PassLogin</t>
+  </si>
+  <si>
+    <t>PassConfirm</t>
+  </si>
+  <si>
+    <t>Your new Altoro Mutual Gold VISA with a $10000 and 7.9% APR will be sent in the mail.</t>
+  </si>
+  <si>
+    <t>admin1</t>
+  </si>
+  <si>
+    <t>Login Failed: We're sorry, but this username or password was not found in our system. Please try again.</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Cuenta</t>
+  </si>
+  <si>
+    <t>Mensaje Esperado</t>
+  </si>
+  <si>
+    <t>Account History - 800000 Corporate</t>
+  </si>
+  <si>
+    <t>Account History - 800001 Checking</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -83,6 +150,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -92,7 +180,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -100,11 +188,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -112,6 +215,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -393,14 +504,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.44140625" customWidth="1"/>
     <col min="6" max="6" width="21" customWidth="1"/>
-    <col min="7" max="7" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -420,7 +531,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -440,7 +551,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -460,7 +571,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -484,4 +595,213 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4859881C-930C-4687-A054-D3DAEB399C2A}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A89A9AB-A70E-4D54-A33B-7D0C79C1CE8B}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22.21875" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="21.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="42.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="43.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8C801CC-5B40-4572-9DD8-07776426A289}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E422D674-3FC6-47F4-AB95-ADD9A9F3C06F}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="16.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D6" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>